--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>116161227</v>
       </c>
       <c r="B2" t="n">
-        <v>97733</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134923529</v>
+        <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>91835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511375</v>
+        <v>511223</v>
       </c>
       <c r="R2" t="n">
-        <v>6511719</v>
+        <v>6511710</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,33 +762,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134923529</t>
+          <t>https://artportalen.se/Sighting/136178012</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134922927</v>
+        <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>58415</v>
+        <v>93355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,39 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -855,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511395</v>
+        <v>511256</v>
       </c>
       <c r="R3" t="n">
-        <v>6511620</v>
+        <v>6511697</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,33 +868,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922927</t>
+          <t>https://artportalen.se/Sighting/136177941</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134922217</v>
+        <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>58141</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,35 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511217</v>
+        <v>511402</v>
       </c>
       <c r="R4" t="n">
-        <v>6511696</v>
+        <v>6511621</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,22 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,33 +974,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922217</t>
+          <t>https://artportalen.se/Sighting/136177627</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134923530</v>
+        <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>58141</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,35 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1103,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511375</v>
+        <v>511252</v>
       </c>
       <c r="R5" t="n">
-        <v>6511719</v>
+        <v>6511767</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,69 +1080,61 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134923530</t>
+          <t>https://artportalen.se/Sighting/136178073</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134922216</v>
+        <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>92086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103023</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511217</v>
+        <v>511336</v>
       </c>
       <c r="R6" t="n">
-        <v>6511696</v>
+        <v>6511711</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,22 +1172,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färskt bohål under fruktkropp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,33 +1191,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922216</t>
+          <t>https://artportalen.se/Sighting/136177791</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134922543</v>
+        <v>134923529</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,30 +1226,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1348,13 +1262,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511217</v>
+        <v>511375</v>
       </c>
       <c r="R7" t="n">
-        <v>6511651</v>
+        <v>6511719</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1393,7 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,33 +1333,33 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922543</t>
+          <t>https://artportalen.se/Sighting/134923529</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134923659</v>
+        <v>136177598</v>
       </c>
       <c r="B8" t="n">
-        <v>61536</v>
+        <v>57979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106670</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,17 +1367,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1473,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511339</v>
+        <v>511399</v>
       </c>
       <c r="R8" t="n">
-        <v>6511743</v>
+        <v>6511604</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1503,22 +1412,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,44 +1432,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134923659</t>
+          <t>https://artportalen.se/Sighting/136177598</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134922213</v>
+        <v>136177764</v>
       </c>
       <c r="B9" t="n">
-        <v>56711</v>
+        <v>57979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206046</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1578,16 +1477,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1597,13 +1492,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511217</v>
+        <v>511344</v>
       </c>
       <c r="R9" t="n">
-        <v>6511696</v>
+        <v>6511702</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1627,22 +1522,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,27 +1542,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922213</t>
+          <t>https://artportalen.se/Sighting/136177764</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134922396</v>
+        <v>136177861</v>
       </c>
       <c r="B10" t="n">
-        <v>58844</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,32 +1570,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1718,13 +1602,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511214</v>
+        <v>511273</v>
       </c>
       <c r="R10" t="n">
-        <v>6511665</v>
+        <v>6511682</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,22 +1632,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,27 +1652,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922396</t>
+          <t>https://artportalen.se/Sighting/136177861</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134922398</v>
+        <v>136177912</v>
       </c>
       <c r="B11" t="n">
-        <v>99159</v>
+        <v>57979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,35 +1680,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1842,13 +1712,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511214</v>
+        <v>511263</v>
       </c>
       <c r="R11" t="n">
-        <v>6511665</v>
+        <v>6511701</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1872,22 +1742,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,27 +1762,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922398</t>
+          <t>https://artportalen.se/Sighting/136177912</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134922931</v>
+        <v>136178025</v>
       </c>
       <c r="B12" t="n">
-        <v>111210</v>
+        <v>57979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,27 +1790,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220240</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1958,13 +1822,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511359</v>
+        <v>511198</v>
       </c>
       <c r="R12" t="n">
-        <v>6511577</v>
+        <v>6511714</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1988,22 +1852,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,65 +1872,73 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922931</t>
+          <t>https://artportalen.se/Sighting/136178025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116161227</v>
+        <v>136178034</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>57979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillsjökärret, Ög</t>
+          <t>Nycklekärret, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511259</v>
+        <v>511243</v>
       </c>
       <c r="R13" t="n">
-        <v>6511768</v>
+        <v>6511729</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2100,12 +1962,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2120,27 +1982,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116161227</t>
+          <t>https://artportalen.se/Sighting/136178034</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134921808</v>
+        <v>136178080</v>
       </c>
       <c r="B14" t="n">
-        <v>100854</v>
+        <v>57979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,27 +2010,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222584</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2176,13 +2042,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511153</v>
+        <v>511256</v>
       </c>
       <c r="R14" t="n">
-        <v>6511567</v>
+        <v>6511775</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2206,22 +2072,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2236,27 +2092,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134921808</t>
+          <t>https://artportalen.se/Sighting/136178080</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134922928</v>
+        <v>136178091</v>
       </c>
       <c r="B15" t="n">
-        <v>99519</v>
+        <v>57979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,27 +2120,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222812</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2292,13 +2152,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511359</v>
+        <v>511235</v>
       </c>
       <c r="R15" t="n">
-        <v>6511577</v>
+        <v>6511768</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2322,22 +2182,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2352,16 +2202,1908 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136178091</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134922927</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58415</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>511395</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6511620</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922927</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134922217</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>511217</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6511696</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922217</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134923530</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>511375</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6511719</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134923530</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136177673</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>511363</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6511641</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177673</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134922216</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>511217</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6511696</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922216</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136177709</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>511343</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6511686</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177709</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134922543</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>511217</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6511651</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922543</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134923659</v>
+      </c>
+      <c r="B23" t="n">
+        <v>61536</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>511339</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6511743</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134923659</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134922213</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>511217</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6511696</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922213</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134922396</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58844</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>511214</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6511665</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922396</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134922398</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>511214</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6511665</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922398</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134922931</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111210</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>511359</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6511577</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922931</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>116161227</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lillsjökärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>511259</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6511768</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116161227</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136177610</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106435</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>511400</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6511614</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177610</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134921808</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100854</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>511153</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6511567</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134921808</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134922928</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99519</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>511359</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6511577</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134922928</t>
         </is>
@@ -2383,6 +4125,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136177598</v>
       </c>
       <c r="B8" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136177764</v>
       </c>
       <c r="B9" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136177861</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136177912</v>
       </c>
       <c r="B11" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>136178025</v>
       </c>
       <c r="B12" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136178034</v>
       </c>
       <c r="B13" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136178080</v>
       </c>
       <c r="B14" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136178091</v>
       </c>
       <c r="B15" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136177673</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136177709</v>
       </c>
       <c r="B21" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136177598</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136177764</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136177861</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136177912</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>136178025</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136178034</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136178080</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136178091</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136177673</v>
       </c>
       <c r="B19" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136177709</v>
       </c>
       <c r="B21" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136177598</v>
       </c>
       <c r="B8" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136177764</v>
       </c>
       <c r="B9" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136177861</v>
       </c>
       <c r="B10" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136177912</v>
       </c>
       <c r="B11" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>136178025</v>
       </c>
       <c r="B12" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136178034</v>
       </c>
       <c r="B13" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136178080</v>
       </c>
       <c r="B14" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136178091</v>
       </c>
       <c r="B15" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136177673</v>
       </c>
       <c r="B19" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136177709</v>
       </c>
       <c r="B21" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>91857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136177598</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136177764</v>
       </c>
       <c r="B9" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136177861</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136177912</v>
       </c>
       <c r="B11" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>136178025</v>
       </c>
       <c r="B12" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136178034</v>
       </c>
       <c r="B13" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136178080</v>
       </c>
       <c r="B14" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136178091</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136177673</v>
       </c>
       <c r="B19" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136177709</v>
       </c>
       <c r="B21" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91857</v>
+        <v>91858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136177598</v>
       </c>
       <c r="B8" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136177764</v>
       </c>
       <c r="B9" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136177861</v>
       </c>
       <c r="B10" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136177912</v>
       </c>
       <c r="B11" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>136178025</v>
       </c>
       <c r="B12" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136178034</v>
       </c>
       <c r="B13" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136178080</v>
       </c>
       <c r="B14" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136178091</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136177673</v>
       </c>
       <c r="B19" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136177709</v>
       </c>
       <c r="B21" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
